--- a/CIUDAD/Rendicion_CIUDAD_2026.xlsx
+++ b/CIUDAD/Rendicion_CIUDAD_2026.xlsx
@@ -851,29 +851,29 @@
         <v>1500657</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0</v>
+        <v>176932</v>
       </c>
       <c r="F9" s="6" t="n">
-        <v>2567469</v>
+        <v>2744401</v>
       </c>
       <c r="G9" s="5" t="n">
-        <v>1283735</v>
+        <v>1372201</v>
       </c>
       <c r="H9" s="5" t="n">
         <v>2567469</v>
       </c>
       <c r="I9" s="5" t="n">
-        <v>0</v>
+        <v>176932</v>
       </c>
       <c r="J9" s="7" t="n">
-        <v>-1283734</v>
+        <v>-1195268</v>
       </c>
       <c r="K9" s="8" t="n">
-        <v>1283735</v>
+        <v>1195269</v>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>Chris le debe a Sol $1.283.735</t>
+          <t>Chris le debe a Sol $1.195.269</t>
         </is>
       </c>
     </row>
@@ -895,29 +895,29 @@
         <v>1314709</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0</v>
+        <v>101000</v>
       </c>
       <c r="F10" s="6" t="n">
-        <v>2654854</v>
+        <v>2755854</v>
       </c>
       <c r="G10" s="5" t="n">
-        <v>1327427</v>
+        <v>1377927</v>
       </c>
       <c r="H10" s="5" t="n">
         <v>2654854</v>
       </c>
       <c r="I10" s="5" t="n">
-        <v>0</v>
+        <v>101000</v>
       </c>
       <c r="J10" s="7" t="n">
-        <v>-1327427</v>
+        <v>-1276927</v>
       </c>
       <c r="K10" s="8" t="n">
-        <v>1327427</v>
+        <v>1276927</v>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>Chris le debe a Sol $1.327.427</t>
+          <t>Chris le debe a Sol $1.276.927</t>
         </is>
       </c>
     </row>
@@ -939,29 +939,29 @@
         <v>585071</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0</v>
+        <v>155800</v>
       </c>
       <c r="F11" s="6" t="n">
-        <v>1172762</v>
+        <v>1328562</v>
       </c>
       <c r="G11" s="5" t="n">
-        <v>586381</v>
+        <v>664281</v>
       </c>
       <c r="H11" s="5" t="n">
         <v>1172762</v>
       </c>
       <c r="I11" s="5" t="n">
-        <v>0</v>
+        <v>155800</v>
       </c>
       <c r="J11" s="7" t="n">
-        <v>-586381</v>
+        <v>-508481</v>
       </c>
       <c r="K11" s="8" t="n">
-        <v>586381</v>
+        <v>508481</v>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>Chris le debe a Sol $586.381</t>
+          <t>Chris le debe a Sol $508.481</t>
         </is>
       </c>
     </row>
@@ -1199,13 +1199,13 @@
         <v>8234788</v>
       </c>
       <c r="E17" s="6" t="n">
-        <v>0</v>
+        <v>433732</v>
       </c>
       <c r="F17" s="6" t="n">
-        <v>15341082</v>
+        <v>15774814</v>
       </c>
       <c r="G17" s="6" t="n">
-        <v>7670541</v>
+        <v>7887407</v>
       </c>
       <c r="H17" s="15" t="n"/>
       <c r="I17" s="15" t="n"/>
@@ -1266,7 +1266,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G43"/>
+  <dimension ref="A1:G46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1288,7 +1288,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TOTAL $1.172.762 · Cada uno $586.381 · Pagó Sol $1.172.762 · Pagó Chris $0</t>
+          <t>TOTAL $1.328.562 · Cada uno $664.281 · Pagó Sol $1.172.762 · Pagó Chris $155.800</t>
         </is>
       </c>
     </row>
@@ -1347,10 +1347,10 @@
         <v>585071</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0</v>
+        <v>155800</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>585071</v>
+        <v>740871</v>
       </c>
     </row>
     <row r="8">
@@ -1363,10 +1363,10 @@
         <v>1172762</v>
       </c>
       <c r="C8" s="21" t="n">
-        <v>0</v>
+        <v>155800</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>1172762</v>
+        <v>1328562</v>
       </c>
     </row>
     <row r="9">
@@ -1376,13 +1376,13 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>586381</v>
+        <v>664281</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>586381</v>
+        <v>664281</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>1172762</v>
+        <v>1328562</v>
       </c>
     </row>
     <row r="10">
@@ -1392,17 +1392,17 @@
         </is>
       </c>
       <c r="B10" s="21" t="n">
-        <v>-586381</v>
+        <v>-508481</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>586381</v>
+        <v>508481</v>
       </c>
       <c r="D10" s="20" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>→ Chris le debe a Sol $586.381</t>
+          <t>→ Chris le debe a Sol $508.481</t>
         </is>
       </c>
     </row>
@@ -1536,257 +1536,233 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="14" t="inlineStr">
+      <c r="A20" s="23" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>ALMACEN</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>ALMACEN CHRIS</t>
+        </is>
+      </c>
+      <c r="D20" s="24" t="n">
+        <v>155800</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B20" s="4" t="n"/>
-      <c r="C20" s="4" t="n"/>
-      <c r="D20" s="6" t="n">
-        <v>1172762</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="22" t="inlineStr">
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="6" t="n">
+        <v>1328562</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="22" t="inlineStr">
         <is>
           <t>Almacén — por familia</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="18" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="18" t="inlineStr">
         <is>
           <t>Familia</t>
         </is>
       </c>
-      <c r="B23" s="18" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>Almacén Sol</t>
         </is>
       </c>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="C24" s="18" t="inlineStr">
         <is>
           <t>Almacén Chris</t>
         </is>
       </c>
-      <c r="D23" s="18" t="inlineStr">
+      <c r="D24" s="18" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>COMIDA</t>
-        </is>
-      </c>
-      <c r="B24" s="5" t="n">
-        <v>478421</v>
-      </c>
-      <c r="C24" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>478421</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
         <is>
+          <t>COMIDA</t>
+        </is>
+      </c>
+      <c r="B25" s="5" t="n">
+        <v>478421</v>
+      </c>
+      <c r="C25" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>478421</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="inlineStr">
+        <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>155800</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>155800</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
           <t>RAMÓN</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n">
+      <c r="B27" s="5" t="n">
         <v>106650</v>
       </c>
-      <c r="C25" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="6" t="n">
+      <c r="C27" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" s="6" t="n">
         <v>106650</v>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="14" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
         <is>
           <t>TOTAL ALMACÉN</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
+      <c r="B28" s="6" t="n">
         <v>585071</v>
       </c>
-      <c r="C26" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>585071</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="22" t="inlineStr">
+      <c r="C28" s="6" t="n">
+        <v>155800</v>
+      </c>
+      <c r="D28" s="6" t="n">
+        <v>740871</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="22" t="inlineStr">
         <is>
           <t>Almacén — detalle día a día</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="18" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="18" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B29" s="18" t="inlineStr">
+      <c r="B31" s="18" t="inlineStr">
         <is>
           <t>Familia</t>
         </is>
       </c>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="C31" s="18" t="inlineStr">
         <is>
           <t>Detalle</t>
         </is>
       </c>
-      <c r="D29" s="18" t="inlineStr">
+      <c r="D31" s="18" t="inlineStr">
         <is>
           <t>Importe Sol</t>
         </is>
       </c>
-      <c r="E29" s="18" t="inlineStr">
+      <c r="E31" s="18" t="inlineStr">
         <is>
           <t>Importe Chris</t>
         </is>
       </c>
-      <c r="F29" s="18" t="inlineStr">
+      <c r="F31" s="18" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="G29" s="18" t="inlineStr">
+      <c r="G31" s="18" t="inlineStr">
         <is>
           <t>Comentario</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="25" t="n">
-        <v>46205</v>
-      </c>
-      <c r="B30" s="4" t="inlineStr">
-        <is>
-          <t>RAMÓN</t>
-        </is>
-      </c>
-      <c r="C30" s="4" t="inlineStr">
-        <is>
-          <t>RAMON · Veterinario</t>
-        </is>
-      </c>
-      <c r="D30" s="5" t="n">
-        <v>106650</v>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="5" t="n">
-        <v>106650</v>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>RAMON · Veterinario · Valeria Mele / El Perro Verde · ALMACEN SOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="25" t="n">
-        <v>46206</v>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>COMIDA</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>COMIDA · Todo Tartas</t>
-        </is>
-      </c>
-      <c r="D31" s="5" t="n">
-        <v>9690</v>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F31" s="5" t="n">
-        <v>9690</v>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>MP · panadería · ex `Todo Tartas`</t>
-        </is>
-      </c>
-    </row>
     <row r="32">
-      <c r="A32" s="25" t="n">
-        <v>46207</v>
-      </c>
+      <c r="A32" s="25" t="n"/>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>COMIDA</t>
+          <t>OTROS</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA</t>
+          <t>Almacén</t>
         </is>
       </c>
       <c r="D32" s="5" t="n">
-        <v>31799</v>
+        <v>0</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>0</v>
+        <v>155800</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>31799</v>
+        <v>155800</v>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA</t>
+          <t>ALMACEN CHRIS</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="25" t="n">
-        <v>46207</v>
+        <v>46205</v>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>COMIDA</t>
+          <t>RAMÓN</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA · propina</t>
+          <t>RAMON · Veterinario</t>
         </is>
       </c>
       <c r="D33" s="5" t="n">
-        <v>1200</v>
+        <v>106650</v>
       </c>
       <c r="E33" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="5" t="n">
-        <v>1200</v>
+        <v>106650</v>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA · propina</t>
+          <t>RAMON · Veterinario · Valeria Mele / El Perro Verde · ALMACEN SOL</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="25" t="n">
-        <v>46209</v>
+        <v>46206</v>
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
@@ -1795,27 +1771,27 @@
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Le Pain Quotidien</t>
+          <t>COMIDA · Todo Tartas</t>
         </is>
       </c>
       <c r="D34" s="5" t="n">
-        <v>3295</v>
+        <v>9690</v>
       </c>
       <c r="E34" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F34" s="5" t="n">
-        <v>3295</v>
+        <v>9690</v>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>MP · panadería · ex `Le Pain Quotidien`</t>
+          <t>MP · panadería · ex `Todo Tartas`</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="25" t="n">
-        <v>46212</v>
+        <v>46207</v>
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
@@ -1824,27 +1800,27 @@
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · VALENTI SA</t>
+          <t>PEDIDOS YA · COMIDA</t>
         </is>
       </c>
       <c r="D35" s="5" t="n">
-        <v>26400</v>
+        <v>31799</v>
       </c>
       <c r="E35" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="5" t="n">
-        <v>26400</v>
+        <v>31799</v>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · VALENTI SA</t>
+          <t>PEDIDOS YA · COMIDA</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="25" t="n">
-        <v>46214</v>
+        <v>46207</v>
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
@@ -1853,27 +1829,27 @@
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · SUSHI</t>
+          <t>PEDIDOS YA · COMIDA · propina</t>
         </is>
       </c>
       <c r="D36" s="5" t="n">
-        <v>195360</v>
+        <v>1200</v>
       </c>
       <c r="E36" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="5" t="n">
-        <v>195360</v>
+        <v>1200</v>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · SUSHI</t>
+          <t>PEDIDOS YA · COMIDA · propina</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="25" t="n">
-        <v>46214</v>
+        <v>46209</v>
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
@@ -1882,27 +1858,27 @@
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · VALENTI SA</t>
+          <t>COMIDA · Le Pain Quotidien</t>
         </is>
       </c>
       <c r="D37" s="5" t="n">
-        <v>11375</v>
+        <v>3295</v>
       </c>
       <c r="E37" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>11375</v>
+        <v>3295</v>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · VALENTI SA</t>
+          <t>MP · panadería · ex `Le Pain Quotidien`</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="25" t="n">
-        <v>46215</v>
+        <v>46212</v>
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
@@ -1911,27 +1887,27 @@
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Barritas proteicas</t>
+          <t>COMIDA · VALENTI SA</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>66527</v>
+        <v>26400</v>
       </c>
       <c r="E38" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>66527</v>
+        <v>26400</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Barritas proteicas · Enerfit · TC Mercado Pago · SALUD · MERPAGO*ENERFIT · TC Mercado Pago · cuota 8 de 12 · compra 2025-11-26 · ex `SALUD · Enerfit · C.08/12`</t>
+          <t>COMIDA · VALENTI SA</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="25" t="n">
-        <v>46216</v>
+        <v>46214</v>
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
@@ -1940,27 +1916,27 @@
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Carnes Tito</t>
+          <t>COMIDA · SUSHI</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>8160</v>
+        <v>195360</v>
       </c>
       <c r="E39" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>8160</v>
+        <v>195360</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>MP · carnicería · ex `Carnes Tito`</t>
+          <t>COMIDA · SUSHI</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="25" t="n">
-        <v>46217</v>
+        <v>46214</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
@@ -1969,27 +1945,27 @@
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · VERDULERÍA</t>
+          <t>COMIDA · VALENTI SA</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>8977</v>
+        <v>11375</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>8977</v>
+        <v>11375</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · VERDULERÍA</t>
+          <t>COMIDA · VALENTI SA</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="25" t="n">
-        <v>46220</v>
+        <v>46215</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
@@ -1998,27 +1974,27 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Chocolates CHIAZZA</t>
+          <t>COMIDA · Barritas proteicas</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>8000</v>
+        <v>66527</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>8000</v>
+        <v>66527</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Chocolates CHIAZZA</t>
+          <t>COMIDA · Barritas proteicas · Enerfit · TC Mercado Pago · SALUD · MERPAGO*ENERFIT · TC Mercado Pago · cuota 8 de 12 · compra 2025-11-26 · ex `SALUD · Enerfit · C.08/12`</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="25" t="n">
-        <v>46220</v>
+        <v>46216</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
@@ -2027,48 +2003,135 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA</t>
+          <t>COMIDA · Carnes Tito</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>73345</v>
+        <v>8160</v>
       </c>
       <c r="E42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>73345</v>
+        <v>8160</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA</t>
+          <t>MP · carnicería · ex `Carnes Tito`</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="25" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>COMIDA</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>COMIDA · VERDULERÍA</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>8977</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>8977</v>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>COMIDA · VERDULERÍA</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="25" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>COMIDA</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>COMIDA · Chocolates CHIAZZA</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="5" t="n">
+        <v>8000</v>
+      </c>
+      <c r="G44" s="4" t="inlineStr">
+        <is>
+          <t>COMIDA · Chocolates CHIAZZA</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="25" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>COMIDA</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>PEDIDOS YA · COMIDA</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>73345</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="5" t="n">
+        <v>73345</v>
+      </c>
+      <c r="G45" s="4" t="inlineStr">
+        <is>
+          <t>PEDIDOS YA · COMIDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="25" t="n">
         <v>46221</v>
       </c>
-      <c r="B43" s="4" t="inlineStr">
+      <c r="B46" s="4" t="inlineStr">
         <is>
           <t>COMIDA</t>
         </is>
       </c>
-      <c r="C43" s="4" t="inlineStr">
+      <c r="C46" s="4" t="inlineStr">
         <is>
           <t>COMIDA · pollo</t>
         </is>
       </c>
-      <c r="D43" s="5" t="n">
+      <c r="D46" s="5" t="n">
         <v>34293</v>
       </c>
-      <c r="E43" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="5" t="n">
+      <c r="E46" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="5" t="n">
         <v>34293</v>
       </c>
-      <c r="G43" s="4" t="inlineStr">
+      <c r="G46" s="4" t="inlineStr">
         <is>
           <t>COMIDA · pollo · MP · pollo · BBVA Visa crédito</t>
         </is>
@@ -3402,10 +3465,10 @@
         <v>1500657</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>0</v>
+        <v>176932</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>1500657</v>
+        <v>1677589</v>
       </c>
     </row>
     <row r="9">
@@ -3418,10 +3481,10 @@
         <v>1314709</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>0</v>
+        <v>101000</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>1314709</v>
+        <v>1415709</v>
       </c>
     </row>
     <row r="10">
@@ -3434,10 +3497,10 @@
         <v>585071</v>
       </c>
       <c r="C10" s="5" t="n">
-        <v>0</v>
+        <v>155800</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>585071</v>
+        <v>740871</v>
       </c>
     </row>
     <row r="11">
@@ -3530,10 +3593,10 @@
         <v>8234788</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>0</v>
+        <v>433732</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>8234788</v>
+        <v>8668520</v>
       </c>
     </row>
   </sheetData>
@@ -4083,10 +4146,10 @@
         <v>0</v>
       </c>
       <c r="C12" s="5" t="n">
-        <v>0</v>
+        <v>433732</v>
       </c>
       <c r="D12" s="6" t="n">
-        <v>0</v>
+        <v>433732</v>
       </c>
       <c r="E12" s="5" t="n">
         <v>0</v>
@@ -4101,13 +4164,13 @@
         <v>0</v>
       </c>
       <c r="I12" s="5" t="n">
-        <v>0</v>
+        <v>176932</v>
       </c>
       <c r="J12" s="5" t="n">
-        <v>0</v>
+        <v>101000</v>
       </c>
       <c r="K12" s="5" t="n">
-        <v>0</v>
+        <v>155800</v>
       </c>
       <c r="L12" s="5" t="n">
         <v>0</v>
@@ -4135,10 +4198,10 @@
         <v>8234788</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>0</v>
+        <v>433732</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>8234788</v>
+        <v>8668520</v>
       </c>
       <c r="E13" s="6" t="n">
         <v>1267198</v>
@@ -4153,13 +4216,13 @@
         <v>1374704</v>
       </c>
       <c r="I13" s="6" t="n">
-        <v>1500657</v>
+        <v>1677589</v>
       </c>
       <c r="J13" s="6" t="n">
-        <v>1314709</v>
+        <v>1415709</v>
       </c>
       <c r="K13" s="6" t="n">
-        <v>585071</v>
+        <v>740871</v>
       </c>
       <c r="L13" s="6" t="n">
         <v>0</v>
@@ -10241,7 +10304,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -10263,7 +10326,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TOTAL $2.567.469 · Cada uno $1.283.735 · Pagó Sol $2.567.469 · Pagó Chris $0</t>
+          <t>TOTAL $2.744.401 · Cada uno $1.372.201 · Pagó Sol $2.567.469 · Pagó Chris $176.932</t>
         </is>
       </c>
     </row>
@@ -10322,10 +10385,10 @@
         <v>1500657</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0</v>
+        <v>176932</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1500657</v>
+        <v>1677589</v>
       </c>
     </row>
     <row r="8">
@@ -10338,10 +10401,10 @@
         <v>2567469</v>
       </c>
       <c r="C8" s="21" t="n">
-        <v>0</v>
+        <v>176932</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>2567469</v>
+        <v>2744401</v>
       </c>
     </row>
     <row r="9">
@@ -10351,13 +10414,13 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1283735</v>
+        <v>1372201</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1283735</v>
+        <v>1372201</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2567469</v>
+        <v>2744401</v>
       </c>
     </row>
     <row r="10">
@@ -10367,17 +10430,17 @@
         </is>
       </c>
       <c r="B10" s="21" t="n">
-        <v>-1283734</v>
+        <v>-1195268</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>1283735</v>
+        <v>1195269</v>
       </c>
       <c r="D10" s="20" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>→ Chris le debe a Sol $1.283.735</t>
+          <t>→ Chris le debe a Sol $1.195.269</t>
         </is>
       </c>
     </row>
@@ -10571,334 +10634,308 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="14" t="inlineStr">
+      <c r="A23" s="23" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>ALMACEN</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>ALMACEN CHRIS</t>
+        </is>
+      </c>
+      <c r="D23" s="24" t="n">
+        <v>176932</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="14" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B23" s="4" t="n"/>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="6" t="n">
-        <v>2567469</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="22" t="inlineStr">
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="6" t="n">
+        <v>2744401</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="22" t="inlineStr">
         <is>
           <t>Almacén — por familia</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="18" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="18" t="inlineStr">
         <is>
           <t>Familia</t>
         </is>
       </c>
-      <c r="B26" s="18" t="inlineStr">
+      <c r="B27" s="18" t="inlineStr">
         <is>
           <t>Almacén Sol</t>
         </is>
       </c>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="C27" s="18" t="inlineStr">
         <is>
           <t>Almacén Chris</t>
         </is>
       </c>
-      <c r="D26" s="18" t="inlineStr">
+      <c r="D27" s="18" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="4" t="inlineStr">
-        <is>
-          <t>SUPERMERCADO</t>
-        </is>
-      </c>
-      <c r="B27" s="5" t="n">
-        <v>472802</v>
-      </c>
-      <c r="C27" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>472802</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO</t>
+          <t>SUPERMERCADO</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>471243</v>
+        <v>472802</v>
       </c>
       <c r="C28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>471243</v>
+        <v>472802</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>RAMÓN</t>
+          <t>ENTRETENIMIENTO</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>380824</v>
+        <v>471243</v>
       </c>
       <c r="C29" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>380824</v>
+        <v>471243</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>COMIDA</t>
+          <t>RAMÓN</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>156034</v>
+        <v>380824</v>
       </c>
       <c r="C30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>156034</v>
+        <v>380824</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
+          <t>OTROS</t>
+        </is>
+      </c>
+      <c r="B31" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="C31" s="5" t="n">
+        <v>176932</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>176932</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>COMIDA</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>156034</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>156034</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
           <t>COMBUSTIBLE</t>
         </is>
       </c>
-      <c r="B31" s="5" t="n">
+      <c r="B33" s="5" t="n">
         <v>19754</v>
       </c>
-      <c r="C31" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D31" s="6" t="n">
+      <c r="C33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="6" t="n">
         <v>19754</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="14" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="14" t="inlineStr">
         <is>
           <t>TOTAL ALMACÉN</t>
         </is>
       </c>
-      <c r="B32" s="6" t="n">
+      <c r="B34" s="6" t="n">
         <v>1500657</v>
       </c>
-      <c r="C32" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="6" t="n">
-        <v>1500657</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="22" t="inlineStr">
+      <c r="C34" s="6" t="n">
+        <v>176932</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>1677589</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
         <is>
           <t>Almacén — detalle día a día</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="18" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B35" s="18" t="inlineStr">
+      <c r="B37" s="18" t="inlineStr">
         <is>
           <t>Familia</t>
         </is>
       </c>
-      <c r="C35" s="18" t="inlineStr">
+      <c r="C37" s="18" t="inlineStr">
         <is>
           <t>Detalle</t>
         </is>
       </c>
-      <c r="D35" s="18" t="inlineStr">
+      <c r="D37" s="18" t="inlineStr">
         <is>
           <t>Importe Sol</t>
         </is>
       </c>
-      <c r="E35" s="18" t="inlineStr">
+      <c r="E37" s="18" t="inlineStr">
         <is>
           <t>Importe Chris</t>
         </is>
       </c>
-      <c r="F35" s="18" t="inlineStr">
+      <c r="F37" s="18" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="G35" s="18" t="inlineStr">
+      <c r="G37" s="18" t="inlineStr">
         <is>
           <t>Comentario</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="25" t="n">
-        <v>46144</v>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>ENTRETENIMIENTO</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>ENTRETENIMIENTO · Cenas</t>
-        </is>
-      </c>
-      <c r="D36" s="5" t="n">
-        <v>30133</v>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="5" t="n">
-        <v>30133</v>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>ENTRETENIMIENTO · Cenas · Cosi Mi Piace (cena) · Mercado Pago · ALMACEN SOL</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="25" t="n">
-        <v>46144</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>SUPERMERCADO</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>PEDIDOS YA · SUPERMERCADO</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>278</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>278</v>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>PEDIDOS YA · SUPERMERCADO · BBVA TC Visa</t>
-        </is>
-      </c>
-    </row>
     <row r="38">
-      <c r="A38" s="25" t="n">
-        <v>46145</v>
-      </c>
+      <c r="A38" s="25" t="n"/>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO</t>
+          <t>OTROS</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO · Teatro</t>
+          <t>Almacén</t>
         </is>
       </c>
       <c r="D38" s="5" t="n">
-        <v>170000</v>
+        <v>0</v>
       </c>
       <c r="E38" s="5" t="n">
-        <v>0</v>
+        <v>80000</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>170000</v>
+        <v>80000</v>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO · Teatro · Plateanet · BBVA VISA · ALMACEN SOL</t>
+          <t>ALMACEN CHRIS</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="25" t="n">
-        <v>46145</v>
-      </c>
+      <c r="A39" s="25" t="n"/>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO</t>
+          <t>OTROS</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO · Teatro</t>
+          <t>Almacén</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>20400</v>
+        <v>0</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>96932</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>20400</v>
+        <v>96932</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO · Teatro · Plateanet · BBVA VISA · ALMACEN SOL</t>
+          <t>ALMACEN CHRIS</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="25" t="n">
-        <v>46147</v>
+        <v>46144</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO</t>
+          <t>ENTRETENIMIENTO</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO</t>
+          <t>ENTRETENIMIENTO · Cenas</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>62267</v>
+        <v>30133</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>62267</v>
+        <v>30133</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO · BBVA TC Visa</t>
+          <t>ENTRETENIMIENTO · Cenas · Cosi Mi Piace (cena) · Mercado Pago · ALMACEN SOL</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="25" t="n">
-        <v>46147</v>
+        <v>46144</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
@@ -10907,85 +10944,85 @@
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO · propina</t>
+          <t>PEDIDOS YA · SUPERMERCADO</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>1000</v>
+        <v>278</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>1000</v>
+        <v>278</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO · propina · BBVA TC Visa</t>
+          <t>PEDIDOS YA · SUPERMERCADO · BBVA TC Visa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="25" t="n">
-        <v>46149</v>
+        <v>46145</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>COMIDA</t>
+          <t>ENTRETENIMIENTO</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Dean &amp; Dennys</t>
+          <t>ENTRETENIMIENTO · Teatro</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>6870</v>
+        <v>170000</v>
       </c>
       <c r="E42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>6870</v>
+        <v>170000</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>MP · comida · ex `Dean &amp; Dennys`</t>
+          <t>ENTRETENIMIENTO · Teatro · Plateanet · BBVA VISA · ALMACEN SOL</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="25" t="n">
-        <v>46149</v>
+        <v>46145</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO</t>
+          <t>ENTRETENIMIENTO</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO</t>
+          <t>ENTRETENIMIENTO · Teatro</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>9594</v>
+        <v>20400</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>9594</v>
+        <v>20400</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO · BBVA TC Visa</t>
+          <t>ENTRETENIMIENTO · Teatro · Plateanet · BBVA VISA · ALMACEN SOL</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="25" t="n">
-        <v>46151</v>
+        <v>46147</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
@@ -10994,56 +11031,56 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO · Coto</t>
+          <t>PEDIDOS YA · SUPERMERCADO</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>47361</v>
+        <v>62267</v>
       </c>
       <c r="E44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>47361</v>
+        <v>62267</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO · Coto</t>
+          <t>PEDIDOS YA · SUPERMERCADO · BBVA TC Visa</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="25" t="n">
-        <v>46153</v>
+        <v>46147</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>RAMÓN</t>
+          <t>SUPERMERCADO</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>RAMON · Veterinario</t>
+          <t>PEDIDOS YA · SUPERMERCADO · propina</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>65700</v>
+        <v>1000</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>65700</v>
+        <v>1000</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>RAMON · Veterinario · Valeria Mele / El Perro Verde · ALMACEN SOL</t>
+          <t>PEDIDOS YA · SUPERMERCADO · propina · BBVA TC Visa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="25" t="n">
-        <v>46154</v>
+        <v>46149</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
@@ -11052,56 +11089,56 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Barritas proteicas</t>
+          <t>COMIDA · Dean &amp; Dennys</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>66527</v>
+        <v>6870</v>
       </c>
       <c r="E46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>66527</v>
+        <v>6870</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Barritas proteicas · Enerfit · TC Mercado Pago · SALUD · MERPAGO*ENERFIT · TC Mercado Pago · cuota 6 de 12 · compra 2025-11-26 · ex `SALUD · Enerfit · C.06/12`</t>
+          <t>MP · comida · ex `Dean &amp; Dennys`</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="25" t="n">
-        <v>46155</v>
+        <v>46149</v>
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>RAMÓN</t>
+          <t>SUPERMERCADO</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>RAMON · Veterinario</t>
+          <t>PEDIDOS YA · SUPERMERCADO</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>21600</v>
+        <v>9594</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>21600</v>
+        <v>9594</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>RAMON · Veterinario · Valeria Mele / El Perro Verde · ALMACEN SOL</t>
+          <t>PEDIDOS YA · SUPERMERCADO · BBVA TC Visa</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="n">
-        <v>46156</v>
+        <v>46151</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
@@ -11110,172 +11147,172 @@
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO</t>
+          <t>SUPERMERCADO · Coto</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>43640</v>
+        <v>47361</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>43640</v>
+        <v>47361</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO · BBVA TC Visa</t>
+          <t>SUPERMERCADO · Coto</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="n">
-        <v>46156</v>
+        <v>46153</v>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO</t>
+          <t>RAMÓN</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO</t>
+          <t>RAMON · Veterinario</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>821</v>
+        <v>65700</v>
       </c>
       <c r="E49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>821</v>
+        <v>65700</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO · BBVA TC Visa</t>
+          <t>RAMON · Veterinario · Valeria Mele / El Perro Verde · ALMACEN SOL</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="n">
-        <v>46156</v>
+        <v>46154</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO</t>
+          <t>COMIDA</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO · propina</t>
+          <t>COMIDA · Barritas proteicas</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>1000</v>
+        <v>66527</v>
       </c>
       <c r="E50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>1000</v>
+        <v>66527</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO · propina · BBVA TC Visa</t>
+          <t>COMIDA · Barritas proteicas · Enerfit · TC Mercado Pago · SALUD · MERPAGO*ENERFIT · TC Mercado Pago · cuota 6 de 12 · compra 2025-11-26 · ex `SALUD · Enerfit · C.06/12`</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="25" t="n">
-        <v>46158</v>
+        <v>46155</v>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>COMIDA</t>
+          <t>RAMÓN</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA</t>
+          <t>RAMON · Veterinario</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>17519</v>
+        <v>21600</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>17519</v>
+        <v>21600</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA</t>
+          <t>RAMON · Veterinario · Valeria Mele / El Perro Verde · ALMACEN SOL</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="25" t="n">
-        <v>46158</v>
+        <v>46156</v>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>COMIDA</t>
+          <t>SUPERMERCADO</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA · propina</t>
+          <t>PEDIDOS YA · SUPERMERCADO</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>1000</v>
+        <v>43640</v>
       </c>
       <c r="E52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>1000</v>
+        <v>43640</v>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA · propina</t>
+          <t>PEDIDOS YA · SUPERMERCADO · BBVA TC Visa</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="25" t="n">
-        <v>46158</v>
+        <v>46156</v>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>RAMÓN</t>
+          <t>SUPERMERCADO</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>RAMON · Veterinario</t>
+          <t>PEDIDOS YA · SUPERMERCADO</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>90000</v>
+        <v>821</v>
       </c>
       <c r="E53" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>90000</v>
+        <v>821</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>RAMON · Veterinario · Valeria Mele / El Perro Verde · ALMACEN SOL</t>
+          <t>PEDIDOS YA · SUPERMERCADO · BBVA TC Visa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="25" t="n">
-        <v>46160</v>
+        <v>46156</v>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
@@ -11284,143 +11321,143 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO</t>
+          <t>PEDIDOS YA · SUPERMERCADO · propina</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>84857</v>
+        <v>1000</v>
       </c>
       <c r="E54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>84857</v>
+        <v>1000</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO · BBVA TC Visa</t>
+          <t>PEDIDOS YA · SUPERMERCADO · propina · BBVA TC Visa</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="25" t="n">
-        <v>46160</v>
+        <v>46158</v>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO</t>
+          <t>COMIDA</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO · propina</t>
+          <t>PEDIDOS YA · COMIDA</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>1200</v>
+        <v>17519</v>
       </c>
       <c r="E55" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>1200</v>
+        <v>17519</v>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO · propina · BBVA TC Visa</t>
+          <t>PEDIDOS YA · COMIDA</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="25" t="n">
-        <v>46160</v>
+        <v>46158</v>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>RAMÓN</t>
+          <t>COMIDA</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>RAMON · Veterinario</t>
+          <t>PEDIDOS YA · COMIDA · propina</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
-        <v>79924</v>
+        <v>1000</v>
       </c>
       <c r="E56" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>79924</v>
+        <v>1000</v>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>RAMON · Veterinario · Leocan · Mercado Pago · ALMACEN SOL</t>
+          <t>PEDIDOS YA · COMIDA · propina</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="25" t="n">
-        <v>46162</v>
+        <v>46158</v>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>COMIDA</t>
+          <t>RAMÓN</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Todo Tartas</t>
+          <t>RAMON · Veterinario</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>3480</v>
+        <v>90000</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>3480</v>
+        <v>90000</v>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>MP · panadería · ex `Todo Tartas`</t>
+          <t>RAMON · Veterinario · Valeria Mele / El Perro Verde · ALMACEN SOL</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="25" t="n">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO</t>
+          <t>SUPERMERCADO</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO · Cine</t>
+          <t>PEDIDOS YA · SUPERMERCADO</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>62200</v>
+        <v>84857</v>
       </c>
       <c r="E58" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>62200</v>
+        <v>84857</v>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO · Cine · Hoyts · BBVA MASTERCARD</t>
+          <t>PEDIDOS YA · SUPERMERCADO · BBVA TC Visa</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="25" t="n">
-        <v>46162</v>
+        <v>46160</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
@@ -11429,85 +11466,85 @@
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO</t>
+          <t>PEDIDOS YA · SUPERMERCADO · propina</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>1936</v>
+        <v>1200</v>
       </c>
       <c r="E59" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>1936</v>
+        <v>1200</v>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO · BBVA TC Visa</t>
+          <t>PEDIDOS YA · SUPERMERCADO · propina · BBVA TC Visa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="25" t="n">
-        <v>46163</v>
+        <v>46160</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO</t>
+          <t>RAMÓN</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO</t>
+          <t>RAMON · Veterinario</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>18339</v>
+        <v>79924</v>
       </c>
       <c r="E60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>18339</v>
+        <v>79924</v>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO · BBVA TC Visa</t>
+          <t>RAMON · Veterinario · Leocan · Mercado Pago · ALMACEN SOL</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="25" t="n">
-        <v>46163</v>
+        <v>46162</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO</t>
+          <t>COMIDA</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO · propina</t>
+          <t>COMIDA · Todo Tartas</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>900</v>
+        <v>3480</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>900</v>
+        <v>3480</v>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · SUPERMERCADO · propina · BBVA TC Visa</t>
+          <t>MP · panadería · ex `Todo Tartas`</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="25" t="n">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
@@ -11516,172 +11553,172 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO · Salidas comida</t>
+          <t>ENTRETENIMIENTO · Cine</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>154100</v>
+        <v>62200</v>
       </c>
       <c r="E62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>154100</v>
+        <v>62200</v>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO · Salidas comida · Hotel Madero (cena) · BBVA · ALMACEN SOL</t>
+          <t>ENTRETENIMIENTO · Cine · Hoyts · BBVA MASTERCARD</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="25" t="n">
-        <v>46164</v>
+        <v>46162</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO</t>
+          <t>SUPERMERCADO</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO · Salidas comida</t>
+          <t>PEDIDOS YA · SUPERMERCADO</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>15410</v>
+        <v>1936</v>
       </c>
       <c r="E63" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>15410</v>
+        <v>1936</v>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO · Salidas comida · Hotel Madero (propina) · BBVA · ALMACEN SOL</t>
+          <t>PEDIDOS YA · SUPERMERCADO · BBVA TC Visa</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="25" t="n">
-        <v>46165</v>
+        <v>46163</v>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>COMIDA</t>
+          <t>SUPERMERCADO</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Arredondo</t>
+          <t>PEDIDOS YA · SUPERMERCADO</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>10290</v>
+        <v>18339</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>10290</v>
+        <v>18339</v>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>MP · Arredondo · QR tienda (almacén OK)</t>
+          <t>PEDIDOS YA · SUPERMERCADO · BBVA TC Visa</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="25" t="n">
-        <v>46165</v>
+        <v>46163</v>
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
-          <t>RAMÓN</t>
+          <t>SUPERMERCADO</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
         <is>
-          <t>RAMON · Veterinario</t>
+          <t>PEDIDOS YA · SUPERMERCADO · propina</t>
         </is>
       </c>
       <c r="D65" s="5" t="n">
-        <v>112500</v>
+        <v>900</v>
       </c>
       <c r="E65" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F65" s="5" t="n">
-        <v>112500</v>
+        <v>900</v>
       </c>
       <c r="G65" s="4" t="inlineStr">
         <is>
-          <t>RAMON · Veterinario · Valeria Mele / El Perro Verde · ALMACEN SOL</t>
+          <t>PEDIDOS YA · SUPERMERCADO · propina · BBVA TC Visa</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="25" t="n">
-        <v>46166</v>
+        <v>46164</v>
       </c>
       <c r="B66" s="4" t="inlineStr">
         <is>
-          <t>COMIDA</t>
+          <t>ENTRETENIMIENTO</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA</t>
+          <t>ENTRETENIMIENTO · Salidas comida</t>
         </is>
       </c>
       <c r="D66" s="5" t="n">
-        <v>21618</v>
+        <v>154100</v>
       </c>
       <c r="E66" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F66" s="5" t="n">
-        <v>21618</v>
+        <v>154100</v>
       </c>
       <c r="G66" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA</t>
+          <t>ENTRETENIMIENTO · Salidas comida · Hotel Madero (cena) · BBVA · ALMACEN SOL</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="25" t="n">
-        <v>46166</v>
+        <v>46164</v>
       </c>
       <c r="B67" s="4" t="inlineStr">
         <is>
-          <t>COMIDA</t>
+          <t>ENTRETENIMIENTO</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA · propina</t>
+          <t>ENTRETENIMIENTO · Salidas comida</t>
         </is>
       </c>
       <c r="D67" s="5" t="n">
-        <v>1100</v>
+        <v>15410</v>
       </c>
       <c r="E67" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>1100</v>
+        <v>15410</v>
       </c>
       <c r="G67" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA · propina</t>
+          <t>ENTRETENIMIENTO · Salidas comida · Hotel Madero (propina) · BBVA · ALMACEN SOL</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="25" t="n">
-        <v>46168</v>
+        <v>46165</v>
       </c>
       <c r="B68" s="4" t="inlineStr">
         <is>
@@ -11690,85 +11727,85 @@
       </c>
       <c r="C68" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Todo Tartas</t>
+          <t>COMIDA · Arredondo</t>
         </is>
       </c>
       <c r="D68" s="5" t="n">
-        <v>8730</v>
+        <v>10290</v>
       </c>
       <c r="E68" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>8730</v>
+        <v>10290</v>
       </c>
       <c r="G68" s="4" t="inlineStr">
         <is>
-          <t>MP · panadería · ex `Todo Tartas`</t>
+          <t>MP · Arredondo · QR tienda (almacén OK)</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="25" t="n">
-        <v>46168</v>
+        <v>46165</v>
       </c>
       <c r="B69" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO</t>
+          <t>RAMÓN</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO · Recitales</t>
+          <t>RAMON · Veterinario</t>
         </is>
       </c>
       <c r="D69" s="5" t="n">
-        <v>19000</v>
+        <v>112500</v>
       </c>
       <c r="E69" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>19000</v>
+        <v>112500</v>
       </c>
       <c r="G69" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO · Recitales · Movistar Arena · Mercado Pago</t>
+          <t>RAMON · Veterinario · Valeria Mele / El Perro Verde · ALMACEN SOL</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="25" t="n">
-        <v>46169</v>
+        <v>46166</v>
       </c>
       <c r="B70" s="4" t="inlineStr">
         <is>
-          <t>RAMÓN</t>
+          <t>COMIDA</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
         <is>
-          <t>RAMON · Otros</t>
+          <t>PEDIDOS YA · COMIDA</t>
         </is>
       </c>
       <c r="D70" s="5" t="n">
-        <v>11100</v>
+        <v>21618</v>
       </c>
       <c r="E70" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>11100</v>
+        <v>21618</v>
       </c>
       <c r="G70" s="4" t="inlineStr">
         <is>
-          <t>RAMON · Otros · Paws Pet Market · Mercado Pago · ALMACEN SOL</t>
+          <t>PEDIDOS YA · COMIDA</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="25" t="n">
-        <v>46170</v>
+        <v>46166</v>
       </c>
       <c r="B71" s="4" t="inlineStr">
         <is>
@@ -11777,137 +11814,137 @@
       </c>
       <c r="C71" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Tienda De Café</t>
+          <t>PEDIDOS YA · COMIDA · propina</t>
         </is>
       </c>
       <c r="D71" s="5" t="n">
-        <v>18900</v>
+        <v>1100</v>
       </c>
       <c r="E71" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>18900</v>
+        <v>1100</v>
       </c>
       <c r="G71" s="4" t="inlineStr">
         <is>
-          <t>MP · café · ex `Tienda De Café`</t>
+          <t>PEDIDOS YA · COMIDA · propina</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="25" t="n">
-        <v>46172</v>
+        <v>46168</v>
       </c>
       <c r="B72" s="4" t="inlineStr">
         <is>
-          <t>COMBUSTIBLE</t>
+          <t>COMIDA</t>
         </is>
       </c>
       <c r="C72" s="4" t="inlineStr">
         <is>
-          <t>Combustible — Shell</t>
+          <t>COMIDA · Todo Tartas</t>
         </is>
       </c>
       <c r="D72" s="5" t="n">
-        <v>18314</v>
+        <v>8730</v>
       </c>
       <c r="E72" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F72" s="5" t="n">
-        <v>18314</v>
+        <v>8730</v>
       </c>
       <c r="G72" s="4" t="inlineStr">
         <is>
-          <t>MP · combustible · nafta · combustible</t>
+          <t>MP · panadería · ex `Todo Tartas`</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="25" t="n">
-        <v>46172</v>
+        <v>46168</v>
       </c>
       <c r="B73" s="4" t="inlineStr">
         <is>
-          <t>COMBUSTIBLE</t>
+          <t>ENTRETENIMIENTO</t>
         </is>
       </c>
       <c r="C73" s="4" t="inlineStr">
         <is>
-          <t>Combustible — Shell</t>
+          <t>ENTRETENIMIENTO · Recitales</t>
         </is>
       </c>
       <c r="D73" s="5" t="n">
-        <v>1415</v>
+        <v>19000</v>
       </c>
       <c r="E73" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F73" s="5" t="n">
-        <v>1415</v>
+        <v>19000</v>
       </c>
       <c r="G73" s="4" t="inlineStr">
         <is>
-          <t>MP · combustible · nafta · combustible</t>
+          <t>ENTRETENIMIENTO · Recitales · Movistar Arena · Mercado Pago</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="25" t="n">
-        <v>46172</v>
+        <v>46169</v>
       </c>
       <c r="B74" s="4" t="inlineStr">
         <is>
-          <t>COMBUSTIBLE</t>
+          <t>RAMÓN</t>
         </is>
       </c>
       <c r="C74" s="4" t="inlineStr">
         <is>
-          <t>Combustible — Shell</t>
+          <t>RAMON · Otros</t>
         </is>
       </c>
       <c r="D74" s="5" t="n">
-        <v>25</v>
+        <v>11100</v>
       </c>
       <c r="E74" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F74" s="5" t="n">
-        <v>25</v>
+        <v>11100</v>
       </c>
       <c r="G74" s="4" t="inlineStr">
         <is>
-          <t>MP · Shell · pago QR</t>
+          <t>RAMON · Otros · Paws Pet Market · Mercado Pago · ALMACEN SOL</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="25" t="n">
-        <v>46172</v>
+        <v>46170</v>
       </c>
       <c r="B75" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO</t>
+          <t>COMIDA</t>
         </is>
       </c>
       <c r="C75" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO · Carrefour</t>
+          <t>COMIDA · Tienda De Café</t>
         </is>
       </c>
       <c r="D75" s="5" t="n">
-        <v>24333</v>
+        <v>18900</v>
       </c>
       <c r="E75" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F75" s="5" t="n">
-        <v>24333</v>
+        <v>18900</v>
       </c>
       <c r="G75" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO · Carrefour</t>
+          <t>MP · café · ex `Tienda De Café`</t>
         </is>
       </c>
     </row>
@@ -11917,24 +11954,140 @@
       </c>
       <c r="B76" s="4" t="inlineStr">
         <is>
+          <t>COMBUSTIBLE</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Combustible — Shell</t>
+        </is>
+      </c>
+      <c r="D76" s="5" t="n">
+        <v>18314</v>
+      </c>
+      <c r="E76" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F76" s="5" t="n">
+        <v>18314</v>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>MP · combustible · nafta · combustible</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="25" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>COMBUSTIBLE</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Combustible — Shell</t>
+        </is>
+      </c>
+      <c r="D77" s="5" t="n">
+        <v>1415</v>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>1415</v>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>MP · combustible · nafta · combustible</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="25" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B78" s="4" t="inlineStr">
+        <is>
+          <t>COMBUSTIBLE</t>
+        </is>
+      </c>
+      <c r="C78" s="4" t="inlineStr">
+        <is>
+          <t>Combustible — Shell</t>
+        </is>
+      </c>
+      <c r="D78" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="E78" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>MP · Shell · pago QR</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="25" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B79" s="4" t="inlineStr">
+        <is>
           <t>SUPERMERCADO</t>
         </is>
       </c>
-      <c r="C76" s="4" t="inlineStr">
+      <c r="C79" s="4" t="inlineStr">
         <is>
           <t>SUPERMERCADO · Carrefour</t>
         </is>
       </c>
-      <c r="D76" s="5" t="n">
+      <c r="D79" s="5" t="n">
+        <v>24333</v>
+      </c>
+      <c r="E79" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F79" s="5" t="n">
+        <v>24333</v>
+      </c>
+      <c r="G79" s="4" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO · Carrefour</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="25" t="n">
+        <v>46172</v>
+      </c>
+      <c r="B80" s="4" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO</t>
+        </is>
+      </c>
+      <c r="C80" s="4" t="inlineStr">
+        <is>
+          <t>SUPERMERCADO · Carrefour</t>
+        </is>
+      </c>
+      <c r="D80" s="5" t="n">
         <v>175276</v>
       </c>
-      <c r="E76" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F76" s="5" t="n">
+      <c r="E80" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F80" s="5" t="n">
         <v>175276</v>
       </c>
-      <c r="G76" s="4" t="inlineStr">
+      <c r="G80" s="4" t="inlineStr">
         <is>
           <t>SUPERMERCADO · Carrefour · BBVA VISA · MERPAGO*CARREFOUR 122905</t>
         </is>
@@ -11951,7 +12104,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G65"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11973,7 +12126,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>TOTAL $2.654.854 · Cada uno $1.327.427 · Pagó Sol $2.654.854 · Pagó Chris $0</t>
+          <t>TOTAL $2.755.854 · Cada uno $1.377.927 · Pagó Sol $2.654.854 · Pagó Chris $101.000</t>
         </is>
       </c>
     </row>
@@ -12032,10 +12185,10 @@
         <v>1314709</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0</v>
+        <v>101000</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>1314709</v>
+        <v>1415709</v>
       </c>
     </row>
     <row r="8">
@@ -12048,10 +12201,10 @@
         <v>2654854</v>
       </c>
       <c r="C8" s="21" t="n">
-        <v>0</v>
+        <v>101000</v>
       </c>
       <c r="D8" s="21" t="n">
-        <v>2654854</v>
+        <v>2755854</v>
       </c>
     </row>
     <row r="9">
@@ -12061,13 +12214,13 @@
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>1327427</v>
+        <v>1377927</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>1327427</v>
+        <v>1377927</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>2654854</v>
+        <v>2755854</v>
       </c>
     </row>
     <row r="10">
@@ -12077,17 +12230,17 @@
         </is>
       </c>
       <c r="B10" s="21" t="n">
-        <v>-1327427</v>
+        <v>-1276927</v>
       </c>
       <c r="C10" s="21" t="n">
-        <v>1327427</v>
+        <v>1276927</v>
       </c>
       <c r="D10" s="20" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="22" t="inlineStr">
         <is>
-          <t>→ Chris le debe a Sol $1.327.427</t>
+          <t>→ Chris le debe a Sol $1.276.927</t>
         </is>
       </c>
     </row>
@@ -12261,366 +12414,342 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="14" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
+          <t>SERVICIOS</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>ALMACEN</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>ALMACEN CHRIS</t>
+        </is>
+      </c>
+      <c r="D22" s="24" t="n">
+        <v>101000</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B22" s="4" t="n"/>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="6" t="n">
-        <v>2654854</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="22" t="inlineStr">
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="6" t="n">
+        <v>2755854</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="22" t="inlineStr">
         <is>
           <t>Almacén — por familia</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="18" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="18" t="inlineStr">
         <is>
           <t>Familia</t>
         </is>
       </c>
-      <c r="B25" s="18" t="inlineStr">
+      <c r="B26" s="18" t="inlineStr">
         <is>
           <t>Almacén Sol</t>
         </is>
       </c>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="C26" s="18" t="inlineStr">
         <is>
           <t>Almacén Chris</t>
         </is>
       </c>
-      <c r="D25" s="18" t="inlineStr">
+      <c r="D26" s="18" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="4" t="inlineStr">
-        <is>
-          <t>COMIDA</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n">
-        <v>522676</v>
-      </c>
-      <c r="C26" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>522676</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO</t>
+          <t>COMIDA</t>
         </is>
       </c>
       <c r="B27" s="5" t="n">
-        <v>372151</v>
+        <v>522676</v>
       </c>
       <c r="C27" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>372151</v>
+        <v>522676</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO</t>
+          <t>SUPERMERCADO</t>
         </is>
       </c>
       <c r="B28" s="5" t="n">
-        <v>206700</v>
+        <v>372151</v>
       </c>
       <c r="C28" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>206700</v>
+        <v>372151</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>RAMÓN</t>
+          <t>ENTRETENIMIENTO</t>
         </is>
       </c>
       <c r="B29" s="5" t="n">
-        <v>113600</v>
+        <v>206700</v>
       </c>
       <c r="C29" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D29" s="6" t="n">
-        <v>113600</v>
+        <v>206700</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>FARMACIA</t>
+          <t>RAMÓN</t>
         </is>
       </c>
       <c r="B30" s="5" t="n">
-        <v>85034</v>
+        <v>113600</v>
       </c>
       <c r="C30" s="5" t="n">
         <v>0</v>
       </c>
       <c r="D30" s="6" t="n">
-        <v>85034</v>
+        <v>113600</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>STREAMING TV</t>
+          <t>OTROS</t>
         </is>
       </c>
       <c r="B31" s="5" t="n">
-        <v>12900</v>
+        <v>0</v>
       </c>
       <c r="C31" s="5" t="n">
-        <v>0</v>
+        <v>101000</v>
       </c>
       <c r="D31" s="6" t="n">
-        <v>12900</v>
+        <v>101000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
         <is>
+          <t>FARMACIA</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n">
+        <v>85034</v>
+      </c>
+      <c r="C32" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>85034</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="inlineStr">
+        <is>
+          <t>STREAMING TV</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n">
+        <v>12900</v>
+      </c>
+      <c r="C33" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>12900</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
           <t>COMBUSTIBLE</t>
         </is>
       </c>
-      <c r="B32" s="5" t="n">
+      <c r="B34" s="5" t="n">
         <v>1648</v>
       </c>
-      <c r="C32" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="6" t="n">
+      <c r="C34" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="6" t="n">
         <v>1648</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="14" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="14" t="inlineStr">
         <is>
           <t>TOTAL ALMACÉN</t>
         </is>
       </c>
-      <c r="B33" s="6" t="n">
+      <c r="B35" s="6" t="n">
         <v>1314709</v>
       </c>
-      <c r="C33" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D33" s="6" t="n">
-        <v>1314709</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="22" t="inlineStr">
+      <c r="C35" s="6" t="n">
+        <v>101000</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>1415709</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="22" t="inlineStr">
         <is>
           <t>Almacén — detalle día a día</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="18" t="inlineStr">
         <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="B36" s="18" t="inlineStr">
+      <c r="B38" s="18" t="inlineStr">
         <is>
           <t>Familia</t>
         </is>
       </c>
-      <c r="C36" s="18" t="inlineStr">
+      <c r="C38" s="18" t="inlineStr">
         <is>
           <t>Detalle</t>
         </is>
       </c>
-      <c r="D36" s="18" t="inlineStr">
+      <c r="D38" s="18" t="inlineStr">
         <is>
           <t>Importe Sol</t>
         </is>
       </c>
-      <c r="E36" s="18" t="inlineStr">
+      <c r="E38" s="18" t="inlineStr">
         <is>
           <t>Importe Chris</t>
         </is>
       </c>
-      <c r="F36" s="18" t="inlineStr">
+      <c r="F38" s="18" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="G36" s="18" t="inlineStr">
+      <c r="G38" s="18" t="inlineStr">
         <is>
           <t>Comentario</t>
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="25" t="n">
-        <v>46174</v>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>COMIDA</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>COMIDA · Huevos Point</t>
-        </is>
-      </c>
-      <c r="D37" s="5" t="n">
-        <v>7500</v>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F37" s="5" t="n">
-        <v>7500</v>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>MP · huevos · ex `Huevos Point`</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="25" t="n">
-        <v>46176</v>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>SUPERMERCADO</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>SUPERMERCADO · Carrefour</t>
-        </is>
-      </c>
-      <c r="D38" s="5" t="n">
-        <v>23943</v>
-      </c>
-      <c r="E38" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>23943</v>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>SUPERMERCADO · Carrefour</t>
-        </is>
-      </c>
-    </row>
     <row r="39">
-      <c r="A39" s="25" t="n">
-        <v>46178</v>
-      </c>
+      <c r="A39" s="25" t="n"/>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>COMIDA</t>
+          <t>OTROS</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Le Pain Quotidien</t>
+          <t>Almacén</t>
         </is>
       </c>
       <c r="D39" s="5" t="n">
-        <v>3432</v>
+        <v>0</v>
       </c>
       <c r="E39" s="5" t="n">
-        <v>0</v>
+        <v>101000</v>
       </c>
       <c r="F39" s="5" t="n">
-        <v>3432</v>
+        <v>101000</v>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>BBVA VISA · ex `COMIDA · MERPAGO*LPQ 757067`</t>
+          <t>ALMACEN CHRIS</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="25" t="n">
-        <v>46180</v>
+        <v>46174</v>
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO</t>
+          <t>COMIDA</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO · Coto</t>
+          <t>COMIDA · Huevos Point</t>
         </is>
       </c>
       <c r="D40" s="5" t="n">
-        <v>348208</v>
+        <v>7500</v>
       </c>
       <c r="E40" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F40" s="5" t="n">
-        <v>348208</v>
+        <v>7500</v>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>SUPERMERCADO · Coto · MP Orden de Venta (único pago 7-jun)</t>
+          <t>MP · huevos · ex `Huevos Point`</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="25" t="n">
-        <v>46184</v>
+        <v>46176</v>
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>COMIDA</t>
+          <t>SUPERMERCADO</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Huevos Point</t>
+          <t>SUPERMERCADO · Carrefour</t>
         </is>
       </c>
       <c r="D41" s="5" t="n">
-        <v>10500</v>
+        <v>23943</v>
       </c>
       <c r="E41" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F41" s="5" t="n">
-        <v>10500</v>
+        <v>23943</v>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>MP · huevos · ex `Huevos Point`</t>
+          <t>SUPERMERCADO · Carrefour</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="25" t="n">
-        <v>46184</v>
+        <v>46178</v>
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
@@ -12629,56 +12758,56 @@
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA</t>
+          <t>COMIDA · Le Pain Quotidien</t>
         </is>
       </c>
       <c r="D42" s="5" t="n">
-        <v>28384</v>
+        <v>3432</v>
       </c>
       <c r="E42" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F42" s="5" t="n">
-        <v>28384</v>
+        <v>3432</v>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA</t>
+          <t>BBVA VISA · ex `COMIDA · MERPAGO*LPQ 757067`</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="25" t="n">
-        <v>46184</v>
+        <v>46180</v>
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>COMIDA</t>
+          <t>SUPERMERCADO</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA · propina</t>
+          <t>SUPERMERCADO · Coto</t>
         </is>
       </c>
       <c r="D43" s="5" t="n">
-        <v>1200</v>
+        <v>348208</v>
       </c>
       <c r="E43" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="5" t="n">
-        <v>1200</v>
+        <v>348208</v>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA · propina</t>
+          <t>SUPERMERCADO · Coto · MP Orden de Venta (único pago 7-jun)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="25" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
@@ -12687,56 +12816,56 @@
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Barritas proteicas</t>
+          <t>COMIDA · Huevos Point</t>
         </is>
       </c>
       <c r="D44" s="5" t="n">
-        <v>66527</v>
+        <v>10500</v>
       </c>
       <c r="E44" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F44" s="5" t="n">
-        <v>66527</v>
+        <v>10500</v>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Barritas proteicas · Enerfit · TC Mercado Pago · SALUD · MERPAGO*ENERFIT · TC Mercado Pago · cuota 7 de 12 · compra 2025-11-26 · ex `SALUD · Enerfit · C.07/12`</t>
+          <t>MP · huevos · ex `Huevos Point`</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="25" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>FARMACIA</t>
+          <t>COMIDA</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>FARMACIA · Farmacity</t>
+          <t>PEDIDOS YA · COMIDA</t>
         </is>
       </c>
       <c r="D45" s="5" t="n">
-        <v>85034</v>
+        <v>28384</v>
       </c>
       <c r="E45" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F45" s="5" t="n">
-        <v>85034</v>
+        <v>28384</v>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>FARMACIA · Farmacity · TC Mercado Pago · compra 2026-05-29 · cobro resumen 2026-06-12 · ex CASA/FARMACIA matriz</t>
+          <t>PEDIDOS YA · COMIDA</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="25" t="n">
-        <v>46185</v>
+        <v>46184</v>
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
@@ -12745,21 +12874,21 @@
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA</t>
+          <t>PEDIDOS YA · COMIDA · propina</t>
         </is>
       </c>
       <c r="D46" s="5" t="n">
-        <v>17189</v>
+        <v>1200</v>
       </c>
       <c r="E46" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F46" s="5" t="n">
-        <v>17189</v>
+        <v>1200</v>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA</t>
+          <t>PEDIDOS YA · COMIDA · propina</t>
         </is>
       </c>
     </row>
@@ -12774,85 +12903,85 @@
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA · propina</t>
+          <t>COMIDA · Barritas proteicas</t>
         </is>
       </c>
       <c r="D47" s="5" t="n">
-        <v>900</v>
+        <v>66527</v>
       </c>
       <c r="E47" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>900</v>
+        <v>66527</v>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA · propina</t>
+          <t>COMIDA · Barritas proteicas · Enerfit · TC Mercado Pago · SALUD · MERPAGO*ENERFIT · TC Mercado Pago · cuota 7 de 12 · compra 2025-11-26 · ex `SALUD · Enerfit · C.07/12`</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="25" t="n">
-        <v>46186</v>
+        <v>46185</v>
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>COMIDA</t>
+          <t>FARMACIA</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Todo Tartas</t>
+          <t>FARMACIA · Farmacity</t>
         </is>
       </c>
       <c r="D48" s="5" t="n">
-        <v>11700</v>
+        <v>85034</v>
       </c>
       <c r="E48" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>11700</v>
+        <v>85034</v>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>MP · panadería · ex `Todo Tartas`</t>
+          <t>FARMACIA · Farmacity · TC Mercado Pago · compra 2026-05-29 · cobro resumen 2026-06-12 · ex CASA/FARMACIA matriz</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="25" t="n">
-        <v>46186</v>
+        <v>46185</v>
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>RAMÓN</t>
+          <t>COMIDA</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>RAMON · Comida</t>
+          <t>PEDIDOS YA · COMIDA</t>
         </is>
       </c>
       <c r="D49" s="5" t="n">
-        <v>65000</v>
+        <v>17189</v>
       </c>
       <c r="E49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="5" t="n">
-        <v>65000</v>
+        <v>17189</v>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>RAMON · Comida · DR BARF · ALMACEN SOL</t>
+          <t>PEDIDOS YA · COMIDA</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="25" t="n">
-        <v>46189</v>
+        <v>46185</v>
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
@@ -12861,27 +12990,27 @@
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA</t>
+          <t>PEDIDOS YA · COMIDA · propina</t>
         </is>
       </c>
       <c r="D50" s="5" t="n">
-        <v>68899</v>
+        <v>900</v>
       </c>
       <c r="E50" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>68899</v>
+        <v>900</v>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA</t>
+          <t>PEDIDOS YA · COMIDA · propina</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="25" t="n">
-        <v>46189</v>
+        <v>46186</v>
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
@@ -12890,56 +13019,56 @@
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA · propina</t>
+          <t>COMIDA · Todo Tartas</t>
         </is>
       </c>
       <c r="D51" s="5" t="n">
-        <v>1200</v>
+        <v>11700</v>
       </c>
       <c r="E51" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F51" s="5" t="n">
-        <v>1200</v>
+        <v>11700</v>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA · propina · MP cuenta</t>
+          <t>MP · panadería · ex `Todo Tartas`</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="25" t="n">
-        <v>46191</v>
+        <v>46186</v>
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>COMIDA</t>
+          <t>RAMÓN</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Tienda De Café</t>
+          <t>RAMON · Comida</t>
         </is>
       </c>
       <c r="D52" s="5" t="n">
-        <v>18700</v>
+        <v>65000</v>
       </c>
       <c r="E52" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F52" s="5" t="n">
-        <v>18700</v>
+        <v>65000</v>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>MP · café · ex `Tienda De Café`</t>
+          <t>RAMON · Comida · DR BARF · ALMACEN SOL</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="25" t="n">
-        <v>46192</v>
+        <v>46189</v>
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
@@ -12948,27 +13077,27 @@
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Todo Tartas</t>
+          <t>PEDIDOS YA · COMIDA</t>
         </is>
       </c>
       <c r="D53" s="5" t="n">
-        <v>28000</v>
+        <v>68899</v>
       </c>
       <c r="E53" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="5" t="n">
-        <v>28000</v>
+        <v>68899</v>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>MP · panadería · ex `Todo Tartas`</t>
+          <t>PEDIDOS YA · COMIDA</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="25" t="n">
-        <v>46193</v>
+        <v>46189</v>
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
@@ -12977,27 +13106,27 @@
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA</t>
+          <t>PEDIDOS YA · COMIDA · propina</t>
         </is>
       </c>
       <c r="D54" s="5" t="n">
-        <v>52902</v>
+        <v>1200</v>
       </c>
       <c r="E54" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="5" t="n">
-        <v>52902</v>
+        <v>1200</v>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA · neto</t>
+          <t>PEDIDOS YA · COMIDA · propina · MP cuenta</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="25" t="n">
-        <v>46193</v>
+        <v>46191</v>
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
@@ -13006,56 +13135,56 @@
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA · propina</t>
+          <t>COMIDA · Tienda De Café</t>
         </is>
       </c>
       <c r="D55" s="5" t="n">
-        <v>1500</v>
+        <v>18700</v>
       </c>
       <c r="E55" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>1500</v>
+        <v>18700</v>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>PEDIDOS YA · COMIDA · propina</t>
+          <t>MP · café · ex `Tienda De Café`</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="25" t="n">
-        <v>46194</v>
+        <v>46192</v>
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>COMBUSTIBLE</t>
+          <t>COMIDA</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>Combustible — Shell</t>
+          <t>COMIDA · Todo Tartas</t>
         </is>
       </c>
       <c r="D56" s="5" t="n">
-        <v>1648</v>
+        <v>28000</v>
       </c>
       <c r="E56" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>1648</v>
+        <v>28000</v>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>MP · combustible · nafta · combustible</t>
+          <t>MP · panadería · ex `Todo Tartas`</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="25" t="n">
-        <v>46195</v>
+        <v>46193</v>
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
@@ -13064,27 +13193,27 @@
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · pollo</t>
+          <t>PEDIDOS YA · COMIDA</t>
         </is>
       </c>
       <c r="D57" s="5" t="n">
-        <v>40939</v>
+        <v>52902</v>
       </c>
       <c r="E57" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F57" s="5" t="n">
-        <v>40939</v>
+        <v>52902</v>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · pollo · MP · pollo</t>
+          <t>PEDIDOS YA · COMIDA · neto</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="25" t="n">
-        <v>46196</v>
+        <v>46193</v>
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
@@ -13093,56 +13222,56 @@
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Buenos Muchachos</t>
+          <t>PEDIDOS YA · COMIDA · propina</t>
         </is>
       </c>
       <c r="D58" s="5" t="n">
-        <v>64750</v>
+        <v>1500</v>
       </c>
       <c r="E58" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>64750</v>
+        <v>1500</v>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Buenos Muchachos Resto · MP cuenta</t>
+          <t>PEDIDOS YA · COMIDA · propina</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="25" t="n">
-        <v>46197</v>
+        <v>46194</v>
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>COMIDA</t>
+          <t>COMBUSTIBLE</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · pollo</t>
+          <t>Combustible — Shell</t>
         </is>
       </c>
       <c r="D59" s="5" t="n">
-        <v>17154</v>
+        <v>1648</v>
       </c>
       <c r="E59" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>17154</v>
+        <v>1648</v>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · pollo · MP · pollo</t>
+          <t>MP · combustible · nafta · combustible</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="25" t="n">
-        <v>46199</v>
+        <v>46195</v>
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
@@ -13151,56 +13280,56 @@
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Todo Tartas</t>
+          <t>COMIDA · pollo</t>
         </is>
       </c>
       <c r="D60" s="5" t="n">
-        <v>23700</v>
+        <v>40939</v>
       </c>
       <c r="E60" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>23700</v>
+        <v>40939</v>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>MP · panadería · ex `Todo Tartas`</t>
+          <t>COMIDA · pollo · MP · pollo</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="25" t="n">
-        <v>46199</v>
+        <v>46196</v>
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>RAMÓN</t>
+          <t>COMIDA</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>RAMON · Veterinario</t>
+          <t>COMIDA · Buenos Muchachos</t>
         </is>
       </c>
       <c r="D61" s="5" t="n">
-        <v>48600</v>
+        <v>64750</v>
       </c>
       <c r="E61" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>48600</v>
+        <v>64750</v>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>RAMON · Veterinario · Valeria Mele / El Perro Verde · ALMACEN SOL</t>
+          <t>COMIDA · Buenos Muchachos Resto · MP cuenta</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="25" t="n">
-        <v>46200</v>
+        <v>46197</v>
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
@@ -13209,27 +13338,27 @@
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Confitería Dos Escudos</t>
+          <t>COMIDA · pollo</t>
         </is>
       </c>
       <c r="D62" s="5" t="n">
-        <v>40600</v>
+        <v>17154</v>
       </c>
       <c r="E62" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>40600</v>
+        <v>17154</v>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>MP · confitería · ex `Confitería Dos Escudos`</t>
+          <t>COMIDA · pollo · MP · pollo</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="25" t="n">
-        <v>46200</v>
+        <v>46199</v>
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
@@ -13238,77 +13367,164 @@
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>COMIDA · Open 25</t>
+          <t>COMIDA · Todo Tartas</t>
         </is>
       </c>
       <c r="D63" s="5" t="n">
-        <v>17000</v>
+        <v>23700</v>
       </c>
       <c r="E63" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>17000</v>
+        <v>23700</v>
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>MP · tienda · ex `Open 25`</t>
+          <t>MP · panadería · ex `Todo Tartas`</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="25" t="n">
-        <v>46200</v>
+        <v>46199</v>
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO</t>
+          <t>RAMÓN</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO · Social</t>
+          <t>RAMON · Veterinario</t>
         </is>
       </c>
       <c r="D64" s="5" t="n">
-        <v>206700</v>
+        <v>48600</v>
       </c>
       <c r="E64" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F64" s="5" t="n">
-        <v>206700</v>
+        <v>48600</v>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>ENTRETENIMIENTO · Social · Belisario Roldán · Mercado Pago</t>
+          <t>RAMON · Veterinario · Valeria Mele / El Perro Verde · ALMACEN SOL</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="25" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B65" s="4" t="inlineStr">
+        <is>
+          <t>COMIDA</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>COMIDA · Confitería Dos Escudos</t>
+        </is>
+      </c>
+      <c r="D65" s="5" t="n">
+        <v>40600</v>
+      </c>
+      <c r="E65" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>40600</v>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>MP · confitería · ex `Confitería Dos Escudos`</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="25" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>COMIDA</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>COMIDA · Open 25</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="n">
+        <v>17000</v>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>17000</v>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>MP · tienda · ex `Open 25`</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="25" t="n">
+        <v>46200</v>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>ENTRETENIMIENTO</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>ENTRETENIMIENTO · Social</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>206700</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>206700</v>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>ENTRETENIMIENTO · Social · Belisario Roldán · Mercado Pago</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="25" t="n">
         <v>46202</v>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>STREAMING TV</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>STREAMING TV</t>
         </is>
       </c>
-      <c r="D65" s="5" t="n">
+      <c r="D68" s="5" t="n">
         <v>12900</v>
       </c>
-      <c r="E65" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="5" t="n">
+      <c r="E68" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="5" t="n">
         <v>12900</v>
       </c>
-      <c r="G65" s="4" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>STREAMING TV · Directv streaming · ALMACEN SOL · resumen MP</t>
         </is>

--- a/CIUDAD/Rendicion_CIUDAD_2026.xlsx
+++ b/CIUDAD/Rendicion_CIUDAD_2026.xlsx
@@ -551,7 +551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K25"/>
+  <dimension ref="A1:K26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -577,7 +577,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generado 2026-09-10 · Fuente: Gastos_CIUDAD_1132_2026.xlsx · Servicios÷2 + Almacén÷2 − lo que cada uno ya pagó → quién le debe a quién</t>
+          <t>Generado 2026-09-11 · Fuente: Gastos_CIUDAD_1132_2026.xlsx · Servicios÷2 + Almacén÷2 − lo que cada uno ya pagó → quién le debe a quién</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="K5" s="4" t="inlineStr">
         <is>
-          <t>Chris le debe a Sol $1.202.668</t>
+          <t>Sin cargo a Chris (aún no pasó almacén)</t>
         </is>
       </c>
     </row>
@@ -716,7 +716,7 @@
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Chris le debe a Sol $961.735</t>
+          <t>Sin cargo a Chris (aún no pasó almacén)</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Chris le debe a Sol $1.053.746</t>
+          <t>Sin cargo a Chris (aún no pasó almacén)</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>Chris le debe a Sol $1.129.851</t>
+          <t>Sin cargo a Chris (aún no pasó almacén)</t>
         </is>
       </c>
     </row>
@@ -1159,7 +1159,7 @@
       <c r="J17" s="11" t="n"/>
       <c r="K17" s="12" t="inlineStr">
         <is>
-          <t>Chris → Sol (meses completos): $7.328.677</t>
+          <t>Chris → Sol (desde 1er mes con almacén Chris): $2.980.677</t>
         </is>
       </c>
     </row>
@@ -1207,6 +1207,13 @@
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
+        <is>
+          <t>• 6) Enero–abril: NO se le cobra nada a Chris (todavía no había pasado gastos de almacén). La deuda arranca en mayo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
         <is>
           <t>• Agosto–diciembre: almacén vacío / Telecentro proyectado — no liquidar hasta completar el mes.</t>
         </is>
@@ -4607,17 +4614,17 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>-1202667</v>
+        <v>0</v>
       </c>
       <c r="C13" s="18" t="n">
-        <v>1202668</v>
+        <v>0</v>
       </c>
       <c r="D13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>→ Chris le debe a Sol $1.202.668</t>
+          <t>→ Sin cargo a Chris (aún no pasó almacén)</t>
         </is>
       </c>
     </row>
@@ -6244,17 +6251,17 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>-961735</v>
+        <v>0</v>
       </c>
       <c r="C13" s="18" t="n">
-        <v>961735</v>
+        <v>0</v>
       </c>
       <c r="D13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>→ Chris le debe a Sol $961.735</t>
+          <t>→ Sin cargo a Chris (aún no pasó almacén)</t>
         </is>
       </c>
     </row>
@@ -7922,17 +7929,17 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>-1053745</v>
+        <v>0</v>
       </c>
       <c r="C13" s="18" t="n">
-        <v>1053746</v>
+        <v>0</v>
       </c>
       <c r="D13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>→ Chris le debe a Sol $1.053.746</t>
+          <t>→ Sin cargo a Chris (aún no pasó almacén)</t>
         </is>
       </c>
     </row>
@@ -9435,17 +9442,17 @@
         </is>
       </c>
       <c r="B13" s="18" t="n">
-        <v>-1129850</v>
+        <v>0</v>
       </c>
       <c r="C13" s="18" t="n">
-        <v>1129851</v>
+        <v>0</v>
       </c>
       <c r="D13" s="17" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>→ Chris le debe a Sol $1.129.851</t>
+          <t>→ Sin cargo a Chris (aún no pasó almacén)</t>
         </is>
       </c>
     </row>

--- a/CIUDAD/Rendicion_CIUDAD_2026.xlsx
+++ b/CIUDAD/Rendicion_CIUDAD_2026.xlsx
@@ -2326,7 +2326,7 @@
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>→ Chris le debe a Sol $25.000</t>
+          <t>→ Mes incompleto — no liquidar aún</t>
         </is>
       </c>
     </row>
@@ -2606,7 +2606,7 @@
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>→ Chris le debe a Sol $25.000</t>
+          <t>→ Mes incompleto — no liquidar aún</t>
         </is>
       </c>
     </row>
@@ -2886,7 +2886,7 @@
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>→ Chris le debe a Sol $25.000</t>
+          <t>→ Mes incompleto — no liquidar aún</t>
         </is>
       </c>
     </row>
@@ -3166,7 +3166,7 @@
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>→ Chris le debe a Sol $25.000</t>
+          <t>→ Mes incompleto — no liquidar aún</t>
         </is>
       </c>
     </row>
@@ -3446,7 +3446,7 @@
     <row r="14">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>→ Chris le debe a Sol $25.000</t>
+          <t>→ Mes incompleto — no liquidar aún</t>
         </is>
       </c>
     </row>
